--- a/sheet/K-Color_시트서식.xlsx
+++ b/sheet/K-Color_시트서식.xlsx
@@ -109,7 +109,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KA-0001</t>
+          <t xml:space="preserve">AD-0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -156,7 +156,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">KE-0001</t>
+          <t xml:space="preserve">ED-2701-CN-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -171,7 +171,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">중국 파트너</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -203,7 +203,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC-0001</t>
+          <t xml:space="preserve">CS-2608KR-001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -218,7 +218,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">서울</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -344,12 +344,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">역할</t>
+          <t xml:space="preserve">코드 접두사</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin / Educator / Consultant  — 이 세 가지 중 하나만 씁니다 (대소문자 무관)</t>
+          <t xml:space="preserve">AD = Admin / ED = Educator / CS = Consultant  — 앞 두 글자로 구분</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -391,12 +391,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">코드 형식</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin = 진단·교육·관리자   Educator = 교육   Consultant = 진단</t>
+          <t xml:space="preserve">자유롭게 쓰셔도 됩니다. AD-0001 · CS-2608KR-001 · ED-2701-CN-002 모두 가능</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -438,12 +438,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">코드</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">KA-0001(Admin) / KE-0001(Educator) / KC-0001(Consultant) 형식을 권장</t>
+          <t xml:space="preserve">앱은 대소문자·하이픈·띄어쓰기를 무시하고 비교합니다</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -485,12 +485,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성여부</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y 면 사용 가능. 그 외 값이면 로그인 차단 (요금 미납 시 여기를 바꾸면 즉시 잠김)</t>
+          <t xml:space="preserve">예) 시트에 AD-0002 라고 적혀 있으면 ad0002 · Ad-0002 · AD 0002 모두 통과</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -532,12 +532,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">만료일</t>
+          <t xml:space="preserve">역할</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">이 날짜가 지나면 로그인 차단</t>
+          <t xml:space="preserve">Admin / Educator / Consultant  — 대소문자 무관. 비워 두면 코드 접두사로 자동 판별</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">최근접속·누적 진단수</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱이 자동으로 채웁니다. 손대지 않아도 됩니다</t>
+          <t xml:space="preserve">Admin = 진단·교육·관리자   Educator = 교육   Consultant = 진단</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -626,12 +626,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">활성여부</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Y 면 사용 가능. 그 외 값이면 로그인 차단 (요금 미납 시 여기를 바꾸면 즉시 잠김)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -673,45 +673,186 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">만료일</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 날짜가 지나면 로그인 차단</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최근접속·누적 진단수</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱이 자동으로 채웁니다. 손대지 않아도 됩니다</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t xml:space="preserve">※ 위 예시 3줄은 운영 전에 지우고 실제 코드를 발급하세요.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -894,7 +1035,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC-0001</t>
+          <t xml:space="preserve">CS-2608KR-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1151,7 +1292,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1227,52 +1368,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">코드 접두사</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AD / ED / CS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Admin · Educator · Consultant</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">유잰</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t xml:space="preserve">※ 이 탭은 기록용입니다. 규칙을 바꾸면 여기에 한 줄 남겨 두세요. 앱 동작에는 영향이 없습니다.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
